--- a/Build/POS.xlsx
+++ b/Build/POS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronica\PicoFX\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4E18BF-1962-479D-B56F-382F3E8EF0ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31EE9854-B0B1-4370-B693-019E1CFD4FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{2FF5DDB3-5F6F-4B26-A214-40B236386A43}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{2FF5DDB3-5F6F-4B26-A214-40B236386A43}"/>
   </bookViews>
   <sheets>
     <sheet name="POS" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="96">
   <si>
     <t>Designator</t>
   </si>
@@ -307,6 +307,12 @@
   </si>
   <si>
     <t>J2</t>
+  </si>
+  <si>
+    <t>R31</t>
+  </si>
+  <si>
+    <t>R32</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9456C5-8C57-459D-A439-BB7A21AA9EC6}">
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -1277,13 +1283,13 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>147.6</v>
+        <v>127.2</v>
       </c>
       <c r="C7">
-        <v>-75.599999999999994</v>
+        <v>-91.8</v>
       </c>
       <c r="D7">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -1294,10 +1300,10 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>127.2</v>
+        <v>148.19999999999999</v>
       </c>
       <c r="C8">
-        <v>-91.8</v>
+        <v>-78.400000000000006</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1311,13 +1317,13 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>144.6</v>
+        <v>127.2</v>
       </c>
       <c r="C9">
-        <v>-71.599999999999994</v>
+        <v>-94.6</v>
       </c>
       <c r="D9">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -1328,13 +1334,13 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>127.2</v>
+        <v>144.6</v>
       </c>
       <c r="C10">
-        <v>-94.6</v>
+        <v>-71.599999999999994</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -1345,13 +1351,13 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>144.6</v>
+        <v>122.8</v>
       </c>
       <c r="C11">
-        <v>-75.599999999999994</v>
+        <v>-100.4</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -1362,13 +1368,13 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>122.8</v>
+        <v>144.6</v>
       </c>
       <c r="C12">
-        <v>-98.4</v>
+        <v>-75.599999999999994</v>
       </c>
       <c r="D12">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -1396,13 +1402,13 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>148.19999999999999</v>
+        <v>135.19999999999999</v>
       </c>
       <c r="C14">
-        <v>-80.599999999999994</v>
+        <v>-100.4</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -1413,13 +1419,13 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>122.8</v>
+        <v>148.19999999999999</v>
       </c>
       <c r="C15">
-        <v>-102.4</v>
+        <v>-80.599999999999994</v>
       </c>
       <c r="D15">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
@@ -2127,10 +2133,10 @@
         <v>59</v>
       </c>
       <c r="B57">
-        <v>128.19999999999999</v>
+        <v>147.6</v>
       </c>
       <c r="C57">
-        <v>-68</v>
+        <v>-75.400000000000006</v>
       </c>
       <c r="D57">
         <v>-90</v>
@@ -2144,13 +2150,13 @@
         <v>60</v>
       </c>
       <c r="B58">
-        <v>138.19999999999999</v>
+        <v>135.19999999999999</v>
       </c>
       <c r="C58">
-        <v>-68</v>
+        <v>-103</v>
       </c>
       <c r="D58">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="E58" t="s">
         <v>6</v>
@@ -2161,13 +2167,13 @@
         <v>61</v>
       </c>
       <c r="B59">
-        <v>125.8</v>
+        <v>128.19999999999999</v>
       </c>
       <c r="C59">
         <v>-68</v>
       </c>
       <c r="D59">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="E59" t="s">
         <v>6</v>
@@ -2178,13 +2184,13 @@
         <v>62</v>
       </c>
       <c r="B60">
-        <v>135.80000000000001</v>
+        <v>138.19999999999999</v>
       </c>
       <c r="C60">
         <v>-68</v>
       </c>
       <c r="D60">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="E60" t="s">
         <v>6</v>
@@ -2195,10 +2201,10 @@
         <v>63</v>
       </c>
       <c r="B61">
-        <v>131</v>
+        <v>125.8</v>
       </c>
       <c r="C61">
-        <v>-74.2</v>
+        <v>-68</v>
       </c>
       <c r="D61">
         <v>90</v>
@@ -2212,10 +2218,10 @@
         <v>64</v>
       </c>
       <c r="B62">
-        <v>133</v>
+        <v>135.80000000000001</v>
       </c>
       <c r="C62">
-        <v>-74.2</v>
+        <v>-68</v>
       </c>
       <c r="D62">
         <v>90</v>
@@ -2229,13 +2235,13 @@
         <v>65</v>
       </c>
       <c r="B63">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C63">
-        <v>-80.400000000000006</v>
+        <v>-74.2</v>
       </c>
       <c r="D63">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="E63" t="s">
         <v>6</v>
@@ -2246,13 +2252,13 @@
         <v>66</v>
       </c>
       <c r="B64">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C64">
-        <v>-80.400000000000006</v>
+        <v>-74.2</v>
       </c>
       <c r="D64">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="E64" t="s">
         <v>6</v>
@@ -2263,13 +2269,13 @@
         <v>67</v>
       </c>
       <c r="B65">
-        <v>157.6</v>
+        <v>127</v>
       </c>
       <c r="C65">
-        <v>-83.8</v>
+        <v>-80.400000000000006</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="E65" t="s">
         <v>6</v>
@@ -2280,13 +2286,13 @@
         <v>68</v>
       </c>
       <c r="B66">
-        <v>157.6</v>
+        <v>137</v>
       </c>
       <c r="C66">
-        <v>-85.4</v>
+        <v>-80.400000000000006</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="E66" t="s">
         <v>6</v>
@@ -2297,10 +2303,10 @@
         <v>69</v>
       </c>
       <c r="B67">
-        <v>168</v>
+        <v>157.6</v>
       </c>
       <c r="C67">
-        <v>-89.6</v>
+        <v>-83.8</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2314,10 +2320,10 @@
         <v>70</v>
       </c>
       <c r="B68">
-        <v>168</v>
+        <v>157.6</v>
       </c>
       <c r="C68">
-        <v>-88</v>
+        <v>-85.4</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2331,10 +2337,10 @@
         <v>71</v>
       </c>
       <c r="B69">
-        <v>164.6</v>
+        <v>168</v>
       </c>
       <c r="C69">
-        <v>-73.400000000000006</v>
+        <v>-89.6</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2348,13 +2354,13 @@
         <v>72</v>
       </c>
       <c r="B70">
-        <v>171.4</v>
+        <v>168</v>
       </c>
       <c r="C70">
-        <v>-73.400000000000006</v>
+        <v>-88</v>
       </c>
       <c r="D70">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E70" t="s">
         <v>6</v>
@@ -2365,13 +2371,13 @@
         <v>73</v>
       </c>
       <c r="B71">
-        <v>161.19999999999999</v>
+        <v>164.6</v>
       </c>
       <c r="C71">
-        <v>-79.599999999999994</v>
+        <v>-73.400000000000006</v>
       </c>
       <c r="D71">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E71" t="s">
         <v>6</v>
@@ -2382,13 +2388,13 @@
         <v>74</v>
       </c>
       <c r="B72">
-        <v>164.6</v>
+        <v>171.4</v>
       </c>
       <c r="C72">
-        <v>-75</v>
+        <v>-73.400000000000006</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E72" t="s">
         <v>6</v>
@@ -2399,7 +2405,7 @@
         <v>75</v>
       </c>
       <c r="B73">
-        <v>174.8</v>
+        <v>161.19999999999999</v>
       </c>
       <c r="C73">
         <v>-79.599999999999994</v>
@@ -2416,13 +2422,13 @@
         <v>76</v>
       </c>
       <c r="B74">
-        <v>171.4</v>
+        <v>164.6</v>
       </c>
       <c r="C74">
         <v>-75</v>
       </c>
       <c r="D74">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E74" t="s">
         <v>6</v>
@@ -2433,13 +2439,13 @@
         <v>77</v>
       </c>
       <c r="B75">
-        <v>162</v>
+        <v>174.8</v>
       </c>
       <c r="C75">
-        <v>-82</v>
+        <v>-79.599999999999994</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E75" t="s">
         <v>6</v>
@@ -2450,10 +2456,10 @@
         <v>78</v>
       </c>
       <c r="B76">
-        <v>174</v>
+        <v>171.4</v>
       </c>
       <c r="C76">
-        <v>-82</v>
+        <v>-75</v>
       </c>
       <c r="D76">
         <v>180</v>
@@ -2467,13 +2473,13 @@
         <v>79</v>
       </c>
       <c r="B77">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C77">
-        <v>-67.2</v>
+        <v>-82</v>
       </c>
       <c r="D77">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E77" t="s">
         <v>6</v>
@@ -2484,13 +2490,13 @@
         <v>80</v>
       </c>
       <c r="B78">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C78">
-        <v>-67.2</v>
+        <v>-82</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E78" t="s">
         <v>6</v>
@@ -2501,7 +2507,7 @@
         <v>81</v>
       </c>
       <c r="B79">
-        <v>161.80000000000001</v>
+        <v>165</v>
       </c>
       <c r="C79">
         <v>-67.2</v>
@@ -2518,7 +2524,7 @@
         <v>82</v>
       </c>
       <c r="B80">
-        <v>174.2</v>
+        <v>171</v>
       </c>
       <c r="C80">
         <v>-67.2</v>
@@ -2535,13 +2541,13 @@
         <v>83</v>
       </c>
       <c r="B81">
-        <v>143.4</v>
+        <v>161.80000000000001</v>
       </c>
       <c r="C81">
-        <v>-101.4</v>
+        <v>-67.2</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E81" t="s">
         <v>6</v>
@@ -2552,10 +2558,10 @@
         <v>84</v>
       </c>
       <c r="B82">
-        <v>143.4</v>
+        <v>174.2</v>
       </c>
       <c r="C82">
-        <v>-99.4</v>
+        <v>-67.2</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2569,13 +2575,13 @@
         <v>85</v>
       </c>
       <c r="B83">
-        <v>156.6</v>
+        <v>143.4</v>
       </c>
       <c r="C83">
-        <v>-91.2</v>
+        <v>-101.4</v>
       </c>
       <c r="D83">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="E83" t="s">
         <v>6</v>
@@ -2586,13 +2592,13 @@
         <v>86</v>
       </c>
       <c r="B84">
-        <v>154.6</v>
+        <v>143.4</v>
       </c>
       <c r="C84">
-        <v>-83</v>
+        <v>-99.4</v>
       </c>
       <c r="D84">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E84" t="s">
         <v>6</v>
@@ -2600,16 +2606,16 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B85">
-        <v>153.80000000000001</v>
+        <v>156.6</v>
       </c>
       <c r="C85">
-        <v>-73.599999999999994</v>
+        <v>-91.2</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="E85" t="s">
         <v>6</v>
@@ -2617,16 +2623,16 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B86">
-        <v>129</v>
+        <v>154.6</v>
       </c>
       <c r="C86">
-        <v>-100.4</v>
+        <v>-83</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E86" t="s">
         <v>6</v>
@@ -2634,13 +2640,13 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B87">
-        <v>132</v>
+        <v>153.80000000000001</v>
       </c>
       <c r="C87">
-        <v>-79</v>
+        <v>-73.599999999999994</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -2651,13 +2657,13 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B88">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="C88">
-        <v>-79</v>
+        <v>-100.4</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -2668,18 +2674,52 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
+        <v>89</v>
+      </c>
+      <c r="B89">
+        <v>132</v>
+      </c>
+      <c r="C89">
+        <v>-79</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>90</v>
+      </c>
+      <c r="B90">
+        <v>168</v>
+      </c>
+      <c r="C90">
+        <v>-79</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
         <v>91</v>
       </c>
-      <c r="B89">
+      <c r="B91">
         <v>150</v>
       </c>
-      <c r="C89">
+      <c r="C91">
         <v>-93.2</v>
       </c>
-      <c r="D89">
+      <c r="D91">
         <v>90</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E91" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Build/POS.xlsx
+++ b/Build/POS.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronica\PicoFX\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31EE9854-B0B1-4370-B693-019E1CFD4FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79A59910-7DC5-453A-A838-43B5F6641C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{2FF5DDB3-5F6F-4B26-A214-40B236386A43}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0B0EBCBB-440C-458C-A423-9C5F2B912AAC}"/>
   </bookViews>
   <sheets>
-    <sheet name="POS" sheetId="1" r:id="rId1"/>
+    <sheet name="PicoFX-all-pos" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,9 +25,276 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="96">
-  <si>
-    <t>Designator</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="94">
+  <si>
+    <t>Ref</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>bottom</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>C22</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>C24</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>C26</t>
+  </si>
+  <si>
+    <t>C27</t>
+  </si>
+  <si>
+    <t>C28</t>
+  </si>
+  <si>
+    <t>C29</t>
+  </si>
+  <si>
+    <t>C30</t>
+  </si>
+  <si>
+    <t>C31</t>
+  </si>
+  <si>
+    <t>C32</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>C35</t>
+  </si>
+  <si>
+    <t>C36</t>
+  </si>
+  <si>
+    <t>C37</t>
+  </si>
+  <si>
+    <t>C38</t>
+  </si>
+  <si>
+    <t>C39</t>
+  </si>
+  <si>
+    <t>C40</t>
+  </si>
+  <si>
+    <t>C41</t>
+  </si>
+  <si>
+    <t>C42</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>FB1</t>
+  </si>
+  <si>
+    <t>FB2</t>
+  </si>
+  <si>
+    <t>FB3</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>R17</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
+    <t>R19</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>R21</t>
+  </si>
+  <si>
+    <t>R22</t>
+  </si>
+  <si>
+    <t>R23</t>
+  </si>
+  <si>
+    <t>R24</t>
+  </si>
+  <si>
+    <t>R25</t>
+  </si>
+  <si>
+    <t>R26</t>
+  </si>
+  <si>
+    <t>R27</t>
+  </si>
+  <si>
+    <t>R28</t>
+  </si>
+  <si>
+    <t>R29</t>
+  </si>
+  <si>
+    <t>R30</t>
+  </si>
+  <si>
+    <t>R31</t>
+  </si>
+  <si>
+    <t>R32</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>U5</t>
   </si>
   <si>
     <t>Mid X</t>
@@ -40,279 +307,6 @@
   </si>
   <si>
     <t>Layer</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>bottom</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>C11</t>
-  </si>
-  <si>
-    <t>C12</t>
-  </si>
-  <si>
-    <t>C13</t>
-  </si>
-  <si>
-    <t>C14</t>
-  </si>
-  <si>
-    <t>C15</t>
-  </si>
-  <si>
-    <t>C16</t>
-  </si>
-  <si>
-    <t>C17</t>
-  </si>
-  <si>
-    <t>C18</t>
-  </si>
-  <si>
-    <t>C19</t>
-  </si>
-  <si>
-    <t>C20</t>
-  </si>
-  <si>
-    <t>C21</t>
-  </si>
-  <si>
-    <t>C22</t>
-  </si>
-  <si>
-    <t>C23</t>
-  </si>
-  <si>
-    <t>C24</t>
-  </si>
-  <si>
-    <t>C25</t>
-  </si>
-  <si>
-    <t>C26</t>
-  </si>
-  <si>
-    <t>C27</t>
-  </si>
-  <si>
-    <t>C28</t>
-  </si>
-  <si>
-    <t>C29</t>
-  </si>
-  <si>
-    <t>C30</t>
-  </si>
-  <si>
-    <t>C31</t>
-  </si>
-  <si>
-    <t>C32</t>
-  </si>
-  <si>
-    <t>C33</t>
-  </si>
-  <si>
-    <t>C34</t>
-  </si>
-  <si>
-    <t>C35</t>
-  </si>
-  <si>
-    <t>C36</t>
-  </si>
-  <si>
-    <t>C37</t>
-  </si>
-  <si>
-    <t>C38</t>
-  </si>
-  <si>
-    <t>C39</t>
-  </si>
-  <si>
-    <t>C40</t>
-  </si>
-  <si>
-    <t>C41</t>
-  </si>
-  <si>
-    <t>C42</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>D3</t>
-  </si>
-  <si>
-    <t>D4</t>
-  </si>
-  <si>
-    <t>D5</t>
-  </si>
-  <si>
-    <t>D6</t>
-  </si>
-  <si>
-    <t>FB1</t>
-  </si>
-  <si>
-    <t>FB2</t>
-  </si>
-  <si>
-    <t>FB3</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>R8</t>
-  </si>
-  <si>
-    <t>R9</t>
-  </si>
-  <si>
-    <t>R10</t>
-  </si>
-  <si>
-    <t>R11</t>
-  </si>
-  <si>
-    <t>R12</t>
-  </si>
-  <si>
-    <t>R13</t>
-  </si>
-  <si>
-    <t>R14</t>
-  </si>
-  <si>
-    <t>R15</t>
-  </si>
-  <si>
-    <t>R16</t>
-  </si>
-  <si>
-    <t>R17</t>
-  </si>
-  <si>
-    <t>R18</t>
-  </si>
-  <si>
-    <t>R19</t>
-  </si>
-  <si>
-    <t>R20</t>
-  </si>
-  <si>
-    <t>R21</t>
-  </si>
-  <si>
-    <t>R22</t>
-  </si>
-  <si>
-    <t>R23</t>
-  </si>
-  <si>
-    <t>R24</t>
-  </si>
-  <si>
-    <t>R25</t>
-  </si>
-  <si>
-    <t>R26</t>
-  </si>
-  <si>
-    <t>R27</t>
-  </si>
-  <si>
-    <t>R28</t>
-  </si>
-  <si>
-    <t>R29</t>
-  </si>
-  <si>
-    <t>R30</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>U4</t>
-  </si>
-  <si>
-    <t>U5</t>
-  </si>
-  <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>J2</t>
-  </si>
-  <si>
-    <t>R31</t>
-  </si>
-  <si>
-    <t>R32</t>
   </si>
 </sst>
 </file>
@@ -1172,8 +1166,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9456C5-8C57-459D-A439-BB7A21AA9EC6}">
-  <dimension ref="A1:E91"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCE1A2EF-6D2E-4A2D-8079-67F3BCBB8B75}">
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -1181,21 +1175,21 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>144.80000000000001</v>
@@ -1207,12 +1201,12 @@
         <v>-90</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>154.80000000000001</v>
@@ -1224,12 +1218,12 @@
         <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>147.6</v>
@@ -1241,12 +1235,12 @@
         <v>-90</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>152.6</v>
@@ -1258,12 +1252,12 @@
         <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>147.6</v>
@@ -1275,63 +1269,63 @@
         <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>127.2</v>
+        <v>127.8</v>
       </c>
       <c r="C7">
         <v>-91.8</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>148.19999999999999</v>
+        <v>147.6</v>
       </c>
       <c r="C8">
-        <v>-78.400000000000006</v>
+        <v>-75.400000000000006</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B9">
-        <v>127.2</v>
+        <v>127.8</v>
       </c>
       <c r="C9">
         <v>-94.6</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>144.6</v>
@@ -1343,29 +1337,29 @@
         <v>180</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B11">
-        <v>122.8</v>
+        <v>125.4</v>
       </c>
       <c r="C11">
-        <v>-100.4</v>
+        <v>-98.4</v>
       </c>
       <c r="D11">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>144.6</v>
@@ -1377,12 +1371,12 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>144.6</v>
@@ -1394,29 +1388,29 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B14">
-        <v>135.19999999999999</v>
+        <v>125.4</v>
       </c>
       <c r="C14">
-        <v>-100.4</v>
+        <v>-102.4</v>
       </c>
       <c r="D14">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>148.19999999999999</v>
@@ -1428,12 +1422,12 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>128.19999999999999</v>
@@ -1445,12 +1439,12 @@
         <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>135.80000000000001</v>
@@ -1462,12 +1456,12 @@
         <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B18">
         <v>125.8</v>
@@ -1479,12 +1473,12 @@
         <v>-90</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B19">
         <v>138.19999999999999</v>
@@ -1496,12 +1490,12 @@
         <v>-90</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B20">
         <v>127</v>
@@ -1513,12 +1507,12 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B21">
         <v>137</v>
@@ -1530,12 +1524,12 @@
         <v>180</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B22">
         <v>132</v>
@@ -1547,12 +1541,12 @@
         <v>180</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B23">
         <v>167</v>
@@ -1564,12 +1558,12 @@
         <v>90</v>
       </c>
       <c r="E23" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B24">
         <v>169</v>
@@ -1581,12 +1575,12 @@
         <v>90</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B25">
         <v>162.80000000000001</v>
@@ -1598,12 +1592,12 @@
         <v>-90</v>
       </c>
       <c r="E25" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B26">
         <v>173.2</v>
@@ -1615,12 +1609,12 @@
         <v>-90</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B27">
         <v>165.2</v>
@@ -1632,12 +1626,12 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B28">
         <v>170.8</v>
@@ -1649,12 +1643,12 @@
         <v>180</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B29">
         <v>161.6</v>
@@ -1666,12 +1660,12 @@
         <v>180</v>
       </c>
       <c r="E29" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B30">
         <v>174.4</v>
@@ -1683,12 +1677,12 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B31">
         <v>168</v>
@@ -1700,12 +1694,12 @@
         <v>180</v>
       </c>
       <c r="E31" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B32">
         <v>151.80000000000001</v>
@@ -1717,12 +1711,12 @@
         <v>180</v>
       </c>
       <c r="E32" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B33">
         <v>148.19999999999999</v>
@@ -1734,12 +1728,12 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B34">
         <v>151.6</v>
@@ -1751,12 +1745,12 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B35">
         <v>148.4</v>
@@ -1768,12 +1762,12 @@
         <v>180</v>
       </c>
       <c r="E35" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B36">
         <v>139</v>
@@ -1785,12 +1779,12 @@
         <v>90</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B37">
         <v>148.4</v>
@@ -1802,12 +1796,12 @@
         <v>180</v>
       </c>
       <c r="E37" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B38">
         <v>143.4</v>
@@ -1819,12 +1813,12 @@
         <v>-90</v>
       </c>
       <c r="E38" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B39">
         <v>151.6</v>
@@ -1836,12 +1830,12 @@
         <v>180</v>
       </c>
       <c r="E39" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B40">
         <v>125</v>
@@ -1853,12 +1847,12 @@
         <v>90</v>
       </c>
       <c r="E40" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B41">
         <v>148.19999999999999</v>
@@ -1870,12 +1864,12 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B42">
         <v>141.4</v>
@@ -1887,12 +1881,12 @@
         <v>-90</v>
       </c>
       <c r="E42" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B43">
         <v>151.80000000000001</v>
@@ -1904,12 +1898,12 @@
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B44">
         <v>150.4</v>
@@ -1921,12 +1915,12 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B45">
         <v>150.4</v>
@@ -1938,12 +1932,12 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B46">
         <v>130.6</v>
@@ -1955,12 +1949,12 @@
         <v>90</v>
       </c>
       <c r="E46" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B47">
         <v>130.6</v>
@@ -1972,12 +1966,12 @@
         <v>-90</v>
       </c>
       <c r="E47" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B48">
         <v>160</v>
@@ -1989,12 +1983,12 @@
         <v>90</v>
       </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B49">
         <v>160</v>
@@ -2006,12 +2000,12 @@
         <v>-90</v>
       </c>
       <c r="E49" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B50">
         <v>146.19999999999999</v>
@@ -2023,15 +2017,15 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B51">
-        <v>124.4</v>
+        <v>130.6</v>
       </c>
       <c r="C51">
         <v>-93.2</v>
@@ -2040,12 +2034,12 @@
         <v>-90</v>
       </c>
       <c r="E51" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B52">
         <v>144.6</v>
@@ -2057,355 +2051,355 @@
         <v>180</v>
       </c>
       <c r="E52" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="B53">
-        <v>161.19999999999999</v>
+        <v>143.4</v>
       </c>
       <c r="C53">
-        <v>-132</v>
+        <v>-95.2</v>
       </c>
       <c r="D53">
         <v>90</v>
       </c>
       <c r="E53" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="B54">
-        <v>137.19999999999999</v>
+        <v>150.6</v>
       </c>
       <c r="C54">
-        <v>-132</v>
+        <v>-67.599999999999994</v>
       </c>
       <c r="D54">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="E54" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B55">
-        <v>143.4</v>
+        <v>148.32499999999999</v>
       </c>
       <c r="C55">
-        <v>-95.2</v>
+        <v>-78.400000000000006</v>
       </c>
       <c r="D55">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B56">
-        <v>150.6</v>
+        <v>125.4</v>
       </c>
       <c r="C56">
-        <v>-67.599999999999994</v>
+        <v>-105.2</v>
       </c>
       <c r="D56">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B57">
-        <v>147.6</v>
+        <v>128.19999999999999</v>
       </c>
       <c r="C57">
-        <v>-75.400000000000006</v>
+        <v>-68</v>
       </c>
       <c r="D57">
         <v>-90</v>
       </c>
       <c r="E57" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B58">
-        <v>135.19999999999999</v>
+        <v>138.19999999999999</v>
       </c>
       <c r="C58">
-        <v>-103</v>
+        <v>-68</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="E58" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B59">
-        <v>128.19999999999999</v>
+        <v>125.8</v>
       </c>
       <c r="C59">
         <v>-68</v>
       </c>
       <c r="D59">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="E59" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B60">
-        <v>138.19999999999999</v>
+        <v>135.80000000000001</v>
       </c>
       <c r="C60">
         <v>-68</v>
       </c>
       <c r="D60">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="E60" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B61">
-        <v>125.8</v>
+        <v>131</v>
       </c>
       <c r="C61">
-        <v>-68</v>
+        <v>-74.2</v>
       </c>
       <c r="D61">
         <v>90</v>
       </c>
       <c r="E61" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B62">
-        <v>135.80000000000001</v>
+        <v>133</v>
       </c>
       <c r="C62">
-        <v>-68</v>
+        <v>-74.2</v>
       </c>
       <c r="D62">
         <v>90</v>
       </c>
       <c r="E62" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B63">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C63">
-        <v>-74.2</v>
+        <v>-80.400000000000006</v>
       </c>
       <c r="D63">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="E63" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B64">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C64">
-        <v>-74.2</v>
+        <v>-80.400000000000006</v>
       </c>
       <c r="D64">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="E64" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B65">
-        <v>127</v>
+        <v>157.6</v>
       </c>
       <c r="C65">
-        <v>-80.400000000000006</v>
+        <v>-83.8</v>
       </c>
       <c r="D65">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B66">
-        <v>137</v>
+        <v>157.6</v>
       </c>
       <c r="C66">
-        <v>-80.400000000000006</v>
+        <v>-85.4</v>
       </c>
       <c r="D66">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B67">
-        <v>157.6</v>
+        <v>168</v>
       </c>
       <c r="C67">
-        <v>-83.8</v>
+        <v>-89.6</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B68">
-        <v>157.6</v>
+        <v>168</v>
       </c>
       <c r="C68">
-        <v>-85.4</v>
+        <v>-88</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B69">
-        <v>168</v>
+        <v>164.6</v>
       </c>
       <c r="C69">
-        <v>-89.6</v>
+        <v>-73.400000000000006</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B70">
-        <v>168</v>
+        <v>171.4</v>
       </c>
       <c r="C70">
-        <v>-88</v>
+        <v>-73.400000000000006</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E70" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B71">
-        <v>164.6</v>
+        <v>161.19999999999999</v>
       </c>
       <c r="C71">
-        <v>-73.400000000000006</v>
+        <v>-79.599999999999994</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E71" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B72">
-        <v>171.4</v>
+        <v>164.6</v>
       </c>
       <c r="C72">
-        <v>-73.400000000000006</v>
+        <v>-75</v>
       </c>
       <c r="D72">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B73">
-        <v>161.19999999999999</v>
+        <v>174.8</v>
       </c>
       <c r="C73">
         <v>-79.599999999999994</v>
@@ -2414,100 +2408,100 @@
         <v>90</v>
       </c>
       <c r="E73" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B74">
-        <v>164.6</v>
+        <v>171.4</v>
       </c>
       <c r="C74">
         <v>-75</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E74" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B75">
-        <v>174.8</v>
+        <v>162</v>
       </c>
       <c r="C75">
-        <v>-79.599999999999994</v>
+        <v>-82</v>
       </c>
       <c r="D75">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B76">
-        <v>171.4</v>
+        <v>174</v>
       </c>
       <c r="C76">
-        <v>-75</v>
+        <v>-82</v>
       </c>
       <c r="D76">
         <v>180</v>
       </c>
       <c r="E76" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B77">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C77">
-        <v>-82</v>
+        <v>-67.2</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E77" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B78">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C78">
-        <v>-82</v>
+        <v>-67.2</v>
       </c>
       <c r="D78">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B79">
-        <v>165</v>
+        <v>161.80000000000001</v>
       </c>
       <c r="C79">
         <v>-67.2</v>
@@ -2516,15 +2510,15 @@
         <v>180</v>
       </c>
       <c r="E79" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B80">
-        <v>171</v>
+        <v>174.2</v>
       </c>
       <c r="C80">
         <v>-67.2</v>
@@ -2533,109 +2527,109 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B81">
-        <v>161.80000000000001</v>
+        <v>143.4</v>
       </c>
       <c r="C81">
-        <v>-67.2</v>
+        <v>-101.4</v>
       </c>
       <c r="D81">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B82">
-        <v>174.2</v>
+        <v>143.4</v>
       </c>
       <c r="C82">
-        <v>-67.2</v>
+        <v>-99.4</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B83">
-        <v>143.4</v>
+        <v>156.6</v>
       </c>
       <c r="C83">
-        <v>-101.4</v>
+        <v>-91.2</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="E83" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B84">
-        <v>143.4</v>
+        <v>154.6</v>
       </c>
       <c r="C84">
-        <v>-99.4</v>
+        <v>-83</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E84" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B85">
-        <v>156.6</v>
+        <v>153.80000000000001</v>
       </c>
       <c r="C85">
-        <v>-91.2</v>
+        <v>-73.599999999999994</v>
       </c>
       <c r="D85">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B86">
-        <v>154.6</v>
+        <v>131.6</v>
       </c>
       <c r="C86">
-        <v>-83</v>
+        <v>-100.4</v>
       </c>
       <c r="D86">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
@@ -2643,16 +2637,16 @@
         <v>87</v>
       </c>
       <c r="B87">
-        <v>153.80000000000001</v>
+        <v>132</v>
       </c>
       <c r="C87">
-        <v>-73.599999999999994</v>
+        <v>-79</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
@@ -2660,16 +2654,16 @@
         <v>88</v>
       </c>
       <c r="B88">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="C88">
-        <v>-100.4</v>
+        <v>-79</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
@@ -2677,50 +2671,16 @@
         <v>89</v>
       </c>
       <c r="B89">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="C89">
-        <v>-79</v>
+        <v>-93.2</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E89" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>90</v>
-      </c>
-      <c r="B90">
-        <v>168</v>
-      </c>
-      <c r="C90">
-        <v>-79</v>
-      </c>
-      <c r="D90">
-        <v>0</v>
-      </c>
-      <c r="E90" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>91</v>
-      </c>
-      <c r="B91">
-        <v>150</v>
-      </c>
-      <c r="C91">
-        <v>-93.2</v>
-      </c>
-      <c r="D91">
-        <v>90</v>
-      </c>
-      <c r="E91" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
